--- a/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.158.xlsx
+++ b/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.158.xlsx
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -867,7 +867,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.158.xlsx
+++ b/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.158.xlsx
@@ -416,14 +416,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y33"/>
+  <dimension ref="A1:Y35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="36" customWidth="1" min="6" max="6"/>
     <col width="35" customWidth="1" min="7" max="7"/>
     <col width="27" customWidth="1" min="8" max="8"/>
@@ -431,13 +431,13 @@
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="60" customWidth="1" min="14" max="14"/>
     <col width="60" customWidth="1" min="15" max="15"/>
     <col width="60" customWidth="1" min="16" max="16"/>
     <col width="60" customWidth="1" min="17" max="17"/>
     <col width="30" customWidth="1" min="18" max="18"/>
-    <col width="29" customWidth="1" min="19" max="19"/>
+    <col width="60" customWidth="1" min="19" max="19"/>
     <col width="30" customWidth="1" min="20" max="20"/>
     <col width="29" customWidth="1" min="21" max="21"/>
     <col width="31" customWidth="1" min="22" max="22"/>
@@ -597,16 +597,20 @@
       <c r="I2" s="1" t="inlineStr"/>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>L67: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR :: Pr Ã¦ ecipe-for Subp Ã¦ na or other process</t>
+          <t>L37: stray/suspicious non-ASCII glyph(s): U+FF1A FULLWIDTH COLON | isolated marker/symbol line :: ：</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L43: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ 9 6 takenby</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE :: [BOM]SCHEDULE OF FEES.</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE :: [BOM]SCHEDULE OF FEES.</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L26: isolated marker/symbol line :: s.</t>
@@ -628,7 +632,11 @@
         </is>
       </c>
       <c r="R2" s="1" t="inlineStr"/>
-      <c r="S2" s="1" t="inlineStr"/>
+      <c r="S2" s="1" t="inlineStr">
+        <is>
+          <t>L43: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • 9 6 takenby</t>
+        </is>
+      </c>
       <c r="T2" s="1" t="inlineStr"/>
       <c r="U2" s="1" t="inlineStr"/>
       <c r="V2" s="1" t="inlineStr"/>
@@ -649,7 +657,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>82</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -660,12 +668,12 @@
       <c r="I3" s="1" t="inlineStr"/>
       <c r="J3" s="1" t="inlineStr">
         <is>
-          <t>L69: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR :: Note.- One Subp Ã¦ na only allowed to each</t>
+          <t>L110: stray/suspicious non-ASCII glyph(s): U+25CF BLACK CIRCLE | isolated marker/symbol line :: ●</t>
         </is>
       </c>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>L61: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Note.â€”This charge is subject to the restrictions of Order</t>
+          <t>L43: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • 9 6 takenby</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr"/>
@@ -723,14 +731,10 @@
       <c r="I4" s="1" t="inlineStr"/>
       <c r="J4" s="1" t="inlineStr">
         <is>
-          <t>L110: stray/suspicious non-ASCII glyph(s): U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: â—�</t>
-        </is>
-      </c>
-      <c r="K4" s="1" t="inlineStr">
-        <is>
-          <t>L69: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Note.â€”See as to this charge Order 20 of January, 1851,</t>
-        </is>
-      </c>
+          <t>L111: stray/suspicious non-ASCII glyph(s): U+FF1A FULLWIDTH COLON | isolated marker/symbol line :: ：</t>
+        </is>
+      </c>
+      <c r="K4" s="1" t="inlineStr"/>
       <c r="L4" s="1" t="inlineStr"/>
       <c r="M4" s="1" t="inlineStr"/>
       <c r="N4" s="1" t="inlineStr">
@@ -771,7 +775,7 @@
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
@@ -781,11 +785,7 @@
       <c r="H5" s="1" t="inlineStr"/>
       <c r="I5" s="1" t="inlineStr"/>
       <c r="J5" s="1" t="inlineStr"/>
-      <c r="K5" s="1" t="inlineStr">
-        <is>
-          <t>L77: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR :: PrÃ¦cipe-for SubpÅ“na or other process, entering</t>
-        </is>
-      </c>
+      <c r="K5" s="1" t="inlineStr"/>
       <c r="L5" s="1" t="inlineStr"/>
       <c r="M5" s="1" t="inlineStr"/>
       <c r="N5" s="1" t="inlineStr">
@@ -836,11 +836,7 @@
       <c r="H6" s="1" t="inlineStr"/>
       <c r="I6" s="1" t="inlineStr"/>
       <c r="J6" s="1" t="inlineStr"/>
-      <c r="K6" s="1" t="inlineStr">
-        <is>
-          <t>L83: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Note.â€”One Subpoena only allowed to each County, which</t>
-        </is>
-      </c>
+      <c r="K6" s="1" t="inlineStr"/>
       <c r="L6" s="1" t="inlineStr"/>
       <c r="M6" s="1" t="inlineStr"/>
       <c r="N6" s="1" t="inlineStr">
@@ -887,11 +883,7 @@
       <c r="H7" s="1" t="inlineStr"/>
       <c r="I7" s="1" t="inlineStr"/>
       <c r="J7" s="1" t="inlineStr"/>
-      <c r="K7" s="1" t="inlineStr">
-        <is>
-          <t>L102: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Note.â€”See Orders of 1850 as to Interrogatories.</t>
-        </is>
-      </c>
+      <c r="K7" s="1" t="inlineStr"/>
       <c r="L7" s="1" t="inlineStr"/>
       <c r="M7" s="1" t="inlineStr"/>
       <c r="N7" s="1" t="inlineStr">
@@ -1022,7 +1014,7 @@
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -1037,7 +1029,7 @@
       <c r="M10" s="1" t="inlineStr"/>
       <c r="N10" s="1" t="inlineStr">
         <is>
-          <t>L38: isolated marker/symbol line :: 1</t>
+          <t>L37: stray/suspicious non-ASCII glyph(s): U+FF1A FULLWIDTH COLON | isolated marker/symbol line :: ：</t>
         </is>
       </c>
       <c r="O10" s="1" t="inlineStr"/>
@@ -1065,7 +1057,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1080,7 +1072,7 @@
       <c r="M11" s="1" t="inlineStr"/>
       <c r="N11" s="1" t="inlineStr">
         <is>
-          <t>L39: isolated marker/symbol line :: 0</t>
+          <t>L38: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O11" s="1" t="inlineStr"/>
@@ -1103,7 +1095,7 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
@@ -1123,7 +1115,7 @@
       <c r="M12" s="1" t="inlineStr"/>
       <c r="N12" s="1" t="inlineStr">
         <is>
-          <t>L45: isolated marker/symbol line :: 151</t>
+          <t>L39: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O12" s="1" t="inlineStr"/>
@@ -1166,7 +1158,7 @@
       <c r="M13" s="1" t="inlineStr"/>
       <c r="N13" s="1" t="inlineStr">
         <is>
-          <t>L78: isolated marker/symbol line :: 0</t>
+          <t>L45: isolated marker/symbol line :: 151</t>
         </is>
       </c>
       <c r="O13" s="1" t="inlineStr"/>
@@ -1194,7 +1186,7 @@
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D14" s="1" t="inlineStr"/>
@@ -1209,7 +1201,7 @@
       <c r="M14" s="1" t="inlineStr"/>
       <c r="N14" s="1" t="inlineStr">
         <is>
-          <t>L79: isolated marker/symbol line :: 6</t>
+          <t>L78: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O14" s="1" t="inlineStr"/>
@@ -1252,7 +1244,7 @@
       <c r="M15" s="1" t="inlineStr"/>
       <c r="N15" s="1" t="inlineStr">
         <is>
-          <t>L82: isolated marker/symbol line :: 0</t>
+          <t>L79: isolated marker/symbol line :: 6</t>
         </is>
       </c>
       <c r="O15" s="1" t="inlineStr"/>
@@ -1295,7 +1287,7 @@
       <c r="M16" s="1" t="inlineStr"/>
       <c r="N16" s="1" t="inlineStr">
         <is>
-          <t>L83: isolated marker/symbol line :: 6</t>
+          <t>L82: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O16" s="1" t="inlineStr"/>
@@ -1338,7 +1330,7 @@
       <c r="M17" s="1" t="inlineStr"/>
       <c r="N17" s="1" t="inlineStr">
         <is>
-          <t>L85: isolated marker/symbol line :: 1</t>
+          <t>L83: isolated marker/symbol line :: 6</t>
         </is>
       </c>
       <c r="O17" s="1" t="inlineStr"/>
@@ -1369,7 +1361,7 @@
       <c r="M18" s="1" t="inlineStr"/>
       <c r="N18" s="1" t="inlineStr">
         <is>
-          <t>L86: isolated marker/symbol line :: 3</t>
+          <t>L85: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O18" s="1" t="inlineStr"/>
@@ -1400,7 +1392,7 @@
       <c r="M19" s="1" t="inlineStr"/>
       <c r="N19" s="1" t="inlineStr">
         <is>
-          <t>L89: isolated marker/symbol line :: 1</t>
+          <t>L86: isolated marker/symbol line :: 3</t>
         </is>
       </c>
       <c r="O19" s="1" t="inlineStr"/>
@@ -1431,7 +1423,7 @@
       <c r="M20" s="1" t="inlineStr"/>
       <c r="N20" s="1" t="inlineStr">
         <is>
-          <t>L91: isolated marker/symbol line :: 1</t>
+          <t>L89: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O20" s="1" t="inlineStr"/>
@@ -1462,7 +1454,7 @@
       <c r="M21" s="1" t="inlineStr"/>
       <c r="N21" s="1" t="inlineStr">
         <is>
-          <t>L92: isolated marker/symbol line :: 3</t>
+          <t>L91: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O21" s="1" t="inlineStr"/>
@@ -1493,7 +1485,7 @@
       <c r="M22" s="1" t="inlineStr"/>
       <c r="N22" s="1" t="inlineStr">
         <is>
-          <t>L110: stray/suspicious non-ASCII glyph(s): U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: â—�</t>
+          <t>L92: isolated marker/symbol line :: 3</t>
         </is>
       </c>
       <c r="O22" s="1" t="inlineStr"/>
@@ -1524,7 +1516,7 @@
       <c r="M23" s="1" t="inlineStr"/>
       <c r="N23" s="1" t="inlineStr">
         <is>
-          <t>L119: symbol-only separator/garbage line :: 5 0</t>
+          <t>L110: stray/suspicious non-ASCII glyph(s): U+25CF BLACK CIRCLE | isolated marker/symbol line :: ●</t>
         </is>
       </c>
       <c r="O23" s="1" t="inlineStr"/>
@@ -1555,7 +1547,7 @@
       <c r="M24" s="1" t="inlineStr"/>
       <c r="N24" s="1" t="inlineStr">
         <is>
-          <t>L120: isolated marker/symbol line :: 5</t>
+          <t>L111: stray/suspicious non-ASCII glyph(s): U+FF1A FULLWIDTH COLON | isolated marker/symbol line :: ：</t>
         </is>
       </c>
       <c r="O24" s="1" t="inlineStr"/>
@@ -1586,7 +1578,7 @@
       <c r="M25" s="1" t="inlineStr"/>
       <c r="N25" s="1" t="inlineStr">
         <is>
-          <t>L121: isolated marker/symbol line :: 0</t>
+          <t>L119: symbol-only separator/garbage line :: 5 0</t>
         </is>
       </c>
       <c r="O25" s="1" t="inlineStr"/>
@@ -1617,7 +1609,7 @@
       <c r="M26" s="1" t="inlineStr"/>
       <c r="N26" s="1" t="inlineStr">
         <is>
-          <t>L124: isolated marker/symbol line :: 5</t>
+          <t>L120: isolated marker/symbol line :: 5</t>
         </is>
       </c>
       <c r="O26" s="1" t="inlineStr"/>
@@ -1648,7 +1640,7 @@
       <c r="M27" s="1" t="inlineStr"/>
       <c r="N27" s="1" t="inlineStr">
         <is>
-          <t>L125: isolated marker/symbol line :: 0</t>
+          <t>L121: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O27" s="1" t="inlineStr"/>
@@ -1679,7 +1671,7 @@
       <c r="M28" s="1" t="inlineStr"/>
       <c r="N28" s="1" t="inlineStr">
         <is>
-          <t>L130: isolated marker/symbol line :: 0</t>
+          <t>L124: isolated marker/symbol line :: 5</t>
         </is>
       </c>
       <c r="O28" s="1" t="inlineStr"/>
@@ -1710,7 +1702,7 @@
       <c r="M29" s="1" t="inlineStr"/>
       <c r="N29" s="1" t="inlineStr">
         <is>
-          <t>L131: isolated marker/symbol line :: 6</t>
+          <t>L125: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O29" s="1" t="inlineStr"/>
@@ -1741,7 +1733,7 @@
       <c r="M30" s="1" t="inlineStr"/>
       <c r="N30" s="1" t="inlineStr">
         <is>
-          <t>L133: isolated marker/symbol line :: 0</t>
+          <t>L130: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O30" s="1" t="inlineStr"/>
@@ -1772,7 +1764,7 @@
       <c r="M31" s="1" t="inlineStr"/>
       <c r="N31" s="1" t="inlineStr">
         <is>
-          <t>L134: isolated marker/symbol line :: 6</t>
+          <t>L131: isolated marker/symbol line :: 6</t>
         </is>
       </c>
       <c r="O31" s="1" t="inlineStr"/>
@@ -1803,7 +1795,7 @@
       <c r="M32" s="1" t="inlineStr"/>
       <c r="N32" s="1" t="inlineStr">
         <is>
-          <t>L137: isolated marker/symbol line :: 0</t>
+          <t>L133: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O32" s="1" t="inlineStr"/>
@@ -1834,7 +1826,7 @@
       <c r="M33" s="1" t="inlineStr"/>
       <c r="N33" s="1" t="inlineStr">
         <is>
-          <t>L138: isolated marker/symbol line :: 6</t>
+          <t>L134: isolated marker/symbol line :: 6</t>
         </is>
       </c>
       <c r="O33" s="1" t="inlineStr"/>
@@ -1849,6 +1841,68 @@
       <c r="X33" s="1" t="inlineStr"/>
       <c r="Y33" s="1" t="inlineStr"/>
     </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr"/>
+      <c r="B34" s="1" t="inlineStr"/>
+      <c r="C34" s="1" t="inlineStr"/>
+      <c r="D34" s="1" t="inlineStr"/>
+      <c r="E34" s="1" t="inlineStr"/>
+      <c r="F34" s="1" t="inlineStr"/>
+      <c r="G34" s="1" t="inlineStr"/>
+      <c r="H34" s="1" t="inlineStr"/>
+      <c r="I34" s="1" t="inlineStr"/>
+      <c r="J34" s="1" t="inlineStr"/>
+      <c r="K34" s="1" t="inlineStr"/>
+      <c r="L34" s="1" t="inlineStr"/>
+      <c r="M34" s="1" t="inlineStr"/>
+      <c r="N34" s="1" t="inlineStr">
+        <is>
+          <t>L137: isolated marker/symbol line :: 0</t>
+        </is>
+      </c>
+      <c r="O34" s="1" t="inlineStr"/>
+      <c r="P34" s="1" t="inlineStr"/>
+      <c r="Q34" s="1" t="inlineStr"/>
+      <c r="R34" s="1" t="inlineStr"/>
+      <c r="S34" s="1" t="inlineStr"/>
+      <c r="T34" s="1" t="inlineStr"/>
+      <c r="U34" s="1" t="inlineStr"/>
+      <c r="V34" s="1" t="inlineStr"/>
+      <c r="W34" s="1" t="inlineStr"/>
+      <c r="X34" s="1" t="inlineStr"/>
+      <c r="Y34" s="1" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr"/>
+      <c r="B35" s="1" t="inlineStr"/>
+      <c r="C35" s="1" t="inlineStr"/>
+      <c r="D35" s="1" t="inlineStr"/>
+      <c r="E35" s="1" t="inlineStr"/>
+      <c r="F35" s="1" t="inlineStr"/>
+      <c r="G35" s="1" t="inlineStr"/>
+      <c r="H35" s="1" t="inlineStr"/>
+      <c r="I35" s="1" t="inlineStr"/>
+      <c r="J35" s="1" t="inlineStr"/>
+      <c r="K35" s="1" t="inlineStr"/>
+      <c r="L35" s="1" t="inlineStr"/>
+      <c r="M35" s="1" t="inlineStr"/>
+      <c r="N35" s="1" t="inlineStr">
+        <is>
+          <t>L138: isolated marker/symbol line :: 6</t>
+        </is>
+      </c>
+      <c r="O35" s="1" t="inlineStr"/>
+      <c r="P35" s="1" t="inlineStr"/>
+      <c r="Q35" s="1" t="inlineStr"/>
+      <c r="R35" s="1" t="inlineStr"/>
+      <c r="S35" s="1" t="inlineStr"/>
+      <c r="T35" s="1" t="inlineStr"/>
+      <c r="U35" s="1" t="inlineStr"/>
+      <c r="V35" s="1" t="inlineStr"/>
+      <c r="W35" s="1" t="inlineStr"/>
+      <c r="X35" s="1" t="inlineStr"/>
+      <c r="Y35" s="1" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
